--- a/Sample_run/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Sample_run/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -1107,7 +1107,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>48012</x:v>
+        <x:v>51086</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1723,7 +1723,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>39186</x:v>
+        <x:v>44924</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -2342,7 +2342,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q24" s="0">
-        <x:v>48012</x:v>
+        <x:v>51086</x:v>
       </x:c>
       <x:c r="R24" s="4" t="s">
         <x:v>66</x:v>
@@ -2398,7 +2398,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q25" s="0">
-        <x:v>39186</x:v>
+        <x:v>44924</x:v>
       </x:c>
       <x:c r="R25" s="4" t="s">
         <x:v>66</x:v>
